--- a/artfynd/A 57864-2025 artfynd.xlsx
+++ b/artfynd/A 57864-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130301163</v>
+        <v>130300912</v>
       </c>
       <c r="B2" t="n">
-        <v>98974</v>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>613718</v>
+        <v>613578</v>
       </c>
       <c r="R2" t="n">
-        <v>6903428</v>
+        <v>6903464</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130301177</v>
+        <v>130300599</v>
       </c>
       <c r="B3" t="n">
-        <v>91739</v>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>613720</v>
+        <v>613640</v>
       </c>
       <c r="R3" t="n">
-        <v>6903426</v>
+        <v>6903513</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130301198</v>
+        <v>130301312</v>
       </c>
       <c r="B4" t="n">
-        <v>57864</v>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,42 +880,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ålhustjärnen, Ålhustjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>613736</v>
+        <v>613706</v>
       </c>
       <c r="R4" t="n">
-        <v>6903442</v>
+        <v>6903480</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -971,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130301312</v>
+        <v>130300539</v>
       </c>
       <c r="B5" t="n">
-        <v>91776</v>
+        <v>91872</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>613706</v>
+        <v>613635</v>
       </c>
       <c r="R5" t="n">
-        <v>6903480</v>
+        <v>6903529</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1068,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130300822</v>
+        <v>130301177</v>
       </c>
       <c r="B6" t="n">
-        <v>98974</v>
+        <v>91872</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>613643</v>
+        <v>613720</v>
       </c>
       <c r="R6" t="n">
-        <v>6903454</v>
+        <v>6903426</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1165,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130301098</v>
+        <v>130301988</v>
       </c>
       <c r="B7" t="n">
-        <v>80286</v>
+        <v>79084</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229497</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>613650</v>
+        <v>613660</v>
       </c>
       <c r="R7" t="n">
-        <v>6903428</v>
+        <v>6903566</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1262,48 +1257,53 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130300736</v>
+        <v>130301198</v>
       </c>
       <c r="B8" t="n">
-        <v>98974</v>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Ålhustjärnen, Ålhustjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>613642</v>
+        <v>613736</v>
       </c>
       <c r="R8" t="n">
-        <v>6903468</v>
+        <v>6903442</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1356,6 +1356,801 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>130301912</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Ålhustjärnen, Ålhustjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>613645</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6903551</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Attmar</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>130300561</v>
+      </c>
+      <c r="B10" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Ålhustjärnen, Ålhustjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>613638</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6903510</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Attmar</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>130301970</v>
+      </c>
+      <c r="B11" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Ålhustjärnen, Ålhustjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>613647</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6903549</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Attmar</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>130300736</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Ålhustjärnen, Ålhustjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>613642</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6903468</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Attmar</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>130300822</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Ålhustjärnen, Ålhustjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>613643</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6903454</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Attmar</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>130301163</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Ålhustjärnen, Ålhustjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>613718</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6903428</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Attmar</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>130301098</v>
+      </c>
+      <c r="B15" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Ålhustjärnen, Ålhustjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>613650</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6903428</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Attmar</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>130302059</v>
+      </c>
+      <c r="B16" t="n">
+        <v>92329</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Kötticka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Ålhustjärnen, Ålhustjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>613660</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6903566</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Attmar</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 57864-2025 artfynd.xlsx
+++ b/artfynd/A 57864-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130300912</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130300599</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130301312</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130300539</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130301177</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130301988</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1356,6 +1391,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130301198</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1462,6 +1502,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130301912</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1564,6 +1609,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130300561</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1666,6 +1716,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130301970</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1763,6 +1818,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130300736</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1860,6 +1920,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130300822</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1957,6 +2022,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130301163</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2054,6 +2124,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130301098</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2151,8 +2226,30 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130302059</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>